--- a/src/FR 509-B Suivi pièces master.xlsx
+++ b/src/FR 509-B Suivi pièces master.xlsx
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Date: 25/07/2026</v>
+        <v>Date: 26/07/2026</v>
       </c>
       <c r="B3" t="str">
         <v/>
